--- a/source_data/SourceData_Fig6.xlsx
+++ b/source_data/SourceData_Fig6.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>analysis/supervisor_2026_09_20/nh3_cost_decomposition.csv</t>
+          <t>analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_decomposition.csv</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -657,7 +657,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/supervisor_2026_09_20/nh3_cost_decomposition.csv</t>
+          <t>source: analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_decomposition.csv</t>
         </is>
       </c>
     </row>
@@ -685,10 +685,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.763013253312669</v>
+        <v>1.694105408707456</v>
       </c>
       <c r="C4" t="n">
-        <v>1.319657289321968</v>
+        <v>1.281757974789101</v>
       </c>
     </row>
     <row r="5">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0856707590425556</v>
+        <v>-0.1174003121988346</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3971189174734056</v>
+        <v>0.414570171709359</v>
       </c>
     </row>
     <row r="6">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.73312914875735</v>
+        <v>-0.7874525203733981</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7532210318165425</v>
+        <v>0.7830988862053689</v>
       </c>
     </row>
     <row r="7">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.631667581169177</v>
+        <v>3.987619254399332</v>
       </c>
       <c r="C7" t="n">
-        <v>2.897417169643048</v>
+        <v>2.543190589919633</v>
       </c>
     </row>
     <row r="8">
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.6468395788271044</v>
+        <v>-0.684357760840661</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7057617683549074</v>
+        <v>0.7263967684623636</v>
       </c>
     </row>
     <row r="9">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6291187330945023</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6960153032019762</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.180730030240532</v>
+        <v>1.024451692029646</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9994015166322926</v>
+        <v>0.9134484306163055</v>
       </c>
     </row>
     <row r="11">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.738890111189871</v>
+        <v>5.11696576172354</v>
       </c>
     </row>
     <row r="14">
@@ -1508,11 +1508,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9285714285714284</v>
+        <v>0.9107142857142855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>figures/composite/fig1/fig1_rolling.csv (K = 15)</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (deterministic.rolling) (K = 15)</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>figures/composite/fig1/fig1_rolling.csv (K = 3)</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (deterministic.rolling) (K = 3)</t>
         </is>
       </c>
     </row>

--- a/source_data/SourceData_Fig6.xlsx
+++ b/source_data/SourceData_Fig6.xlsx
@@ -12,8 +12,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="e" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="f" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -435,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Source Data for Fig. 6 (process routes and Au/TiO2 control; renderer figures/composite/fig5/make_fig5.py)</t>
+          <t>Source Data for Fig. 6 (backward design; renderer figures/composite/fig3/make_fig3.py)</t>
         </is>
       </c>
     </row>
@@ -476,15 +474,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NH3: Ru - Fe by cost pool (edge widths)</t>
+          <t>Ru cost vs direct activity multiplier</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_decomposition.csv</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/breakeven_sweep.csv</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>axis shows alpha 0.3-800</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -494,12 +496,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MeOH: local leverage at 5 wt% Re, 250 C (edge widths)</t>
+          <t>lines and bands</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>data/meoh/meoh_candidate_ranking_D01v3.csv</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json; analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_mc_summary.json</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -507,61 +509,61 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Au/TiO2 particles (render)</t>
+          <t>measured activity gains (bottom strip)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>figures/composite/fig5/renders/Au_TiO2_2to6nm.json</t>
+          <t>analysis/promoted_ru_literature_2026_10_05/nh3_1_2/fig3_literature_points.csv</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>labels only; the image is a render</t>
+          <t>P04 is drawn as one point at factor_high, offset below its row</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>activity rank vs catalyst-burden rank</t>
+          <t>lowest feasible Ru cost along the strict E_N scaling line</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data/rank_preservation_control_v1_1.csv</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/scaling_reachability.csv</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ranks 1-5 in file order on both sides</t>
+          <t>rows with a feasible cost</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mass activity and required catalyst vs diameter</t>
+          <t>printed values</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data/rank_preservation_control_v1_1.csv</t>
+          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (backward_reachability)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -569,38 +571,78 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>exact order kept, semi-open extension</t>
+          <t>required recovery vs direct activity multiplier</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>data/rank_preservation_semiopen_v1_3_summary.csv</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>analysis/fe_bridge_backward_2026_09_29/nh3_1_2/activity_lifecycle_certified_boundary.csv</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>alpha &lt;= 3</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>upstream-to-downstream Spearman rho</t>
+          <t>targets at 99 % recovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>see column source</t>
+          <t>analysis/fe_bridge_backward_2026_09_29/nh3_1_2/activity_lifecycle_target_keypoints.csv</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>exact strict-scaling lifecycle boundary</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>analysis/fe_bridge_backward_2026_09_29/nh3_1_2/scaling_lifecycle_exact_global_boundary.csv</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>tested box and parity points</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>analysis/fe_bridge_backward_2026_09_29/nh3_1_2/scaling_lifecycle_exact_summary.json</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -613,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -650,203 +692,1289 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NH3: Ru - Fe by cost pool (edge widths)</t>
+          <t>Ru cost vs direct activity multiplier</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_decomposition.csv</t>
+          <t>source: provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/breakeven_sweep.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>cost_pool</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Ru_minus_Fe_USD_t</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>edge_width_pt</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>axis shows alpha 0.3-800</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>metal_inventory</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1.694105408707456</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.281757974789101</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Ru_cost</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>reactor_base</t>
-        </is>
+      <c r="A5" t="n">
+        <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1174003121988346</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.414570171709359</v>
+        <v>20.68152947181338</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>vessel_pressure_premium</t>
-        </is>
+      <c r="A6" t="n">
+        <v>0.1258925411794167</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.7874525203733981</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.7830988862053689</v>
+        <v>20.27592393832591</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>fresh_compression_electricity</t>
-        </is>
+      <c r="A7" t="n">
+        <v>0.1584893192461113</v>
       </c>
       <c r="B7" t="n">
-        <v>3.987619254399332</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2.543190589919633</v>
+        <v>19.88014715116363</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>recycle_compression_electricity</t>
-        </is>
+      <c r="A8" t="n">
+        <v>0.1995262314968879</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.684357760840661</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7263967684623636</v>
+        <v>19.49350670414761</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>refrigeration_electricity</t>
-        </is>
+      <c r="A9" t="n">
+        <v>0.251188643150958</v>
       </c>
       <c r="B9" t="n">
+        <v>19.11350855539104</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.3162277660168379</v>
+      </c>
+      <c r="B10" t="n">
+        <v>18.74157064867888</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.3981071705534973</v>
+      </c>
+      <c r="B11" t="n">
+        <v>18.37617435734668</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.5011872336272724</v>
+      </c>
+      <c r="B12" t="n">
+        <v>17.99109222038301</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.6309573444801934</v>
+      </c>
+      <c r="B13" t="n">
+        <v>17.52888002245339</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0.7943282347242815</v>
+      </c>
+      <c r="B14" t="n">
+        <v>17.09766310684286</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
+        <v>16.63274935890281</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1.258925411794168</v>
+      </c>
+      <c r="B16" t="n">
+        <v>16.25799711332062</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1.584893192461114</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15.93751554481386</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1.99526231496888</v>
+      </c>
+      <c r="B18" t="n">
+        <v>15.62413719776115</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2.511886431509581</v>
+      </c>
+      <c r="B19" t="n">
+        <v>15.31883354761153</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B20" t="n">
+        <v>15.01835483419082</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3.981071705534973</v>
+      </c>
+      <c r="B21" t="n">
+        <v>14.7269216727954</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5.011872336272725</v>
+      </c>
+      <c r="B22" t="n">
+        <v>14.44578980863959</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6.309573444801933</v>
+      </c>
+      <c r="B23" t="n">
+        <v>14.17391164178946</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7.943282347242818</v>
+      </c>
+      <c r="B24" t="n">
+        <v>13.91081955541578</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" t="n">
+        <v>13.66109278381242</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>12.58925411794168</v>
+      </c>
+      <c r="B26" t="n">
+        <v>13.42446624796132</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>15.84893192461114</v>
+      </c>
+      <c r="B27" t="n">
+        <v>13.20151888799497</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>19.95262314968881</v>
+      </c>
+      <c r="B28" t="n">
+        <v>12.9952244177211</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>25.11886431509582</v>
+      </c>
+      <c r="B29" t="n">
+        <v>12.81216465840052</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>31.6227766016838</v>
+      </c>
+      <c r="B30" t="n">
+        <v>12.63620058519418</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>39.81071705534973</v>
+      </c>
+      <c r="B31" t="n">
+        <v>12.45112941643002</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>50.11872336272725</v>
+      </c>
+      <c r="B32" t="n">
+        <v>12.27339809151852</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>63.09573444801936</v>
+      </c>
+      <c r="B33" t="n">
+        <v>12.12420584799695</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>79.43282347242821</v>
+      </c>
+      <c r="B34" t="n">
+        <v>11.92654810348958</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>100</v>
+      </c>
+      <c r="B35" t="n">
+        <v>11.6516211584086</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125.8925411794168</v>
+      </c>
+      <c r="B36" t="n">
+        <v>11.43319407203439</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>158.4893192461114</v>
+      </c>
+      <c r="B37" t="n">
+        <v>11.25965147990086</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>199.5262314968881</v>
+      </c>
+      <c r="B38" t="n">
+        <v>11.12176639892864</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>251.1886431509582</v>
+      </c>
+      <c r="B39" t="n">
+        <v>11.01126614831115</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>316.227766016838</v>
+      </c>
+      <c r="B40" t="n">
+        <v>10.89864380345705</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>398.1071705534973</v>
+      </c>
+      <c r="B41" t="n">
+        <v>10.78064998075691</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>501.1872336272725</v>
+      </c>
+      <c r="B42" t="n">
+        <v>10.60149104742143</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>630.9573444801937</v>
+      </c>
+      <c r="B43" t="n">
+        <v>10.44390583633159</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>794.3282347242822</v>
+      </c>
+      <c r="B44" t="n">
+        <v>10.29737661826858</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B45" t="n">
+        <v>10.16633211579392</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1258.925411794169</v>
+      </c>
+      <c r="B46" t="n">
+        <v>10.062209269483</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1584.893192461114</v>
+      </c>
+      <c r="B47" t="n">
+        <v>9.958821109833943</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1995.262314968879</v>
+      </c>
+      <c r="B48" t="n">
+        <v>9.843571096480581</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2511.886431509582</v>
+      </c>
+      <c r="B49" t="n">
+        <v>9.677946640163924</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3162.277660168379</v>
+      </c>
+      <c r="B50" t="n">
+        <v>9.501160522681728</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3981.071705534978</v>
+      </c>
+      <c r="B51" t="n">
+        <v>9.360698676033884</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5011.872336272725</v>
+      </c>
+      <c r="B52" t="n">
+        <v>9.232450150338233</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>6309.573444801943</v>
+      </c>
+      <c r="B53" t="n">
+        <v>9.108575990599659</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>7943.282347242822</v>
+      </c>
+      <c r="B54" t="n">
+        <v>9.010149630500983</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B55" t="n">
+        <v>8.931940518320808</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>12589.25411794169</v>
+      </c>
+      <c r="B56" t="n">
+        <v>8.787066274655471</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>15848.93192461114</v>
+      </c>
+      <c r="B57" t="n">
+        <v>8.607362821623905</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>19952.62314968883</v>
+      </c>
+      <c r="B58" t="n">
+        <v>8.464583348015752</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>25118.86431509582</v>
+      </c>
+      <c r="B59" t="n">
+        <v>8.311219153305228</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>31622.77660168379</v>
+      </c>
+      <c r="B60" t="n">
+        <v>8.179932401340796</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>39810.71705534977</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8.075617100081043</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>50118.72336272725</v>
+      </c>
+      <c r="B62" t="n">
+        <v>7.992729428473057</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>63095.73444801943</v>
+      </c>
+      <c r="B63" t="n">
+        <v>7.910441616125598</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>79432.82347242821</v>
+      </c>
+      <c r="B64" t="n">
+        <v>7.829622388955181</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B65" t="n">
+        <v>7.76540168263892</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125892.5411794169</v>
+      </c>
+      <c r="B66" t="n">
+        <v>7.714368325878455</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>158489.3192461114</v>
+      </c>
+      <c r="B67" t="n">
+        <v>7.673812427051581</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>199526.2314968883</v>
+      </c>
+      <c r="B68" t="n">
+        <v>7.641581174856134</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>251188.6431509582</v>
+      </c>
+      <c r="B69" t="n">
+        <v>7.615964292845103</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>316227.7660168379</v>
+      </c>
+      <c r="B70" t="n">
+        <v>7.595603049318648</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>398107.1705534977</v>
+      </c>
+      <c r="B71" t="n">
+        <v>7.579417978286149</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>501187.2336272725</v>
+      </c>
+      <c r="B72" t="n">
+        <v>7.566551463500919</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>630957.3444801943</v>
+      </c>
+      <c r="B73" t="n">
+        <v>7.556322128956163</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>794328.2347242822</v>
+      </c>
+      <c r="B74" t="n">
+        <v>7.548188607855211</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="B75" t="n">
+        <v>7.541720761407087</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>lines and bands</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>source: provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json; analysis/supervisor_2026_09_20/nh3_1_2/nh3_cost_mc_summary.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>alpha* (break-even)</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>114.6671254704968</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Fe cost USD/t</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>11.51578359717927</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ru cost USD/t</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>16.63274935890281</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>strict-scaling max gain (all states)</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1.575275488957531</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>alpha* p05 (cost MC)</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>43.51521000190818</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>alpha* p95 (cost MC)</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>262.2756002000399</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>measured activity gains (bottom strip)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>source: analysis/promoted_ru_literature_2026_10_05/nh3_1_2/fig3_literature_points.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P04 is drawn as one point at factor_high, offset below its row</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>factor_low</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>factor_high</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>lower_bound</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>T_C</t>
+        </is>
+      </c>
+      <c r="J92" s="1" t="inlineStr">
+        <is>
+          <t>P_MPa</t>
+        </is>
+      </c>
+      <c r="K92" s="1" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="L92" s="1" t="inlineStr">
+        <is>
+          <t>y_plotted</t>
+        </is>
+      </c>
+      <c r="M92" s="1" t="inlineStr">
+        <is>
+          <t>x_plotted</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>promoter</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ba–Ru/C</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>75</v>
+      </c>
+      <c r="E93" t="n">
+        <v>75</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>TOF</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>compressor_CAPEX</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1.024451692029646</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.9134484306163055</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5.11696576172354</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>MeOH: local leverage at 5 wt% Re, 250 C (edge widths)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>source: data/meoh/meoh_candidate_ranking_D01v3.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>driver</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>leverage</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>edge_width_pt</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>S_CH4</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.3757939247335326</v>
-      </c>
-      <c r="C17" t="n">
-        <v>2.628803638682398</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>X_CO2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.0588277600606163</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.947338879727499</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STY</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.0028943014647277</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.8405370314111542</v>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>unpromoted Ru/C</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>10.1023/B:CATL.0000016950.09677.4d</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>2</v>
+      </c>
+      <c r="M93" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>promoter</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Cs–Ru/C</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>65</v>
+      </c>
+      <c r="E94" t="n">
+        <v>65</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TOF</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>unpromoted Ru/C</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>10.1023/B:CATL.0000016950.09677.4d</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>2</v>
+      </c>
+      <c r="M94" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>promoter</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ba–Ru/BN, 5 MPa</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" t="n">
+        <v>100</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>per g</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>unpromoted Ru/BN</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>10.1126/science.1064399</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>2</v>
+      </c>
+      <c r="M95" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>promoter</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cs–Ru/MgO</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>30</v>
+      </c>
+      <c r="E96" t="n">
+        <v>134</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>per g</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>unpromoted Ru/MgO</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>300 (&gt;30x); 350 (&gt;134x)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>0.101</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>10.1021/jp066970b</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M96" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>promoter</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Cs–Ru/YSZ</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>per g Ru</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>unpromoted Ru/YSZ</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>0.2-1.1 (1-10 bar gauge)</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>10.1021/acssuschemeng.9b04929</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>2</v>
+      </c>
+      <c r="M97" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ru/C12A7:e⁻</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E98" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>TOF</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Ru/C12A7:O²⁻</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>10.1038/nchem.1476</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>E10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ru/BaTiO2.5H0.5, 5 MPa</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E99" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TOF</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Ru/BaTiO3</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>10.1002/aenm.201801772</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>E09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ru/Ba–Ca(NH2)2</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E100" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>TOF</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Cs–Ru/MgO (promoted)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>10.1002/anie.201712398</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>confinement</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ru inside CNT</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>TOF</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Ru outside CNT</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>10.1002/chem.200902371</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -860,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -897,74 +2025,1750 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Au/TiO2 particles (render)</t>
+          <t>lowest feasible Ru cost along the strict E_N scaling line</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: figures/composite/fig5/renders/Au_TiO2_2to6nm.json</t>
+          <t>source: provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/closure/scaling_reachability.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>labels only; the image is a render</t>
+          <t>rows with a feasible cost</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>diameter_nm</t>
+          <t>E_N_eV</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Au_atoms</t>
+          <t>Ru_min_feasible_cost</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>-1.56</v>
       </c>
       <c r="B5" t="n">
-        <v>155</v>
+        <v>2343.737396236784</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>-1.555</v>
       </c>
       <c r="B6" t="n">
-        <v>626</v>
+        <v>2068.610792143321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>-1.55</v>
       </c>
       <c r="B7" t="n">
-        <v>1525</v>
+        <v>1824.948803975279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>-1.545</v>
       </c>
       <c r="B8" t="n">
-        <v>2999</v>
+        <v>1609.095920209335</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>-1.54</v>
       </c>
       <c r="B9" t="n">
-        <v>5507</v>
+        <v>1417.886276860604</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>-1.535</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1248.497253500977</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1098.417709711001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>-1.525</v>
+      </c>
+      <c r="B12" t="n">
+        <v>965.4716696144708</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="B13" t="n">
+        <v>847.7294020043219</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>-1.515</v>
+      </c>
+      <c r="B14" t="n">
+        <v>743.489583098478</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="B15" t="n">
+        <v>651.2865636578831</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>-1.505</v>
+      </c>
+      <c r="B16" t="n">
+        <v>569.785280840233</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="B17" t="n">
+        <v>497.8072036887403</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>-1.495</v>
+      </c>
+      <c r="B18" t="n">
+        <v>434.3114149765758</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="B19" t="n">
+        <v>378.3777422328575</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>-1.485</v>
+      </c>
+      <c r="B20" t="n">
+        <v>329.1916564857315</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="B21" t="n">
+        <v>286.0307066633926</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>-1.475</v>
+      </c>
+      <c r="B22" t="n">
+        <v>248.252312174187</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="B23" t="n">
+        <v>215.2827966100509</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>-1.465</v>
+      </c>
+      <c r="B24" t="n">
+        <v>186.6076091585729</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="B25" t="n">
+        <v>161.7627398761173</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>-1.455</v>
+      </c>
+      <c r="B26" t="n">
+        <v>140.327378392633</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="B27" t="n">
+        <v>121.9178784147596</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>-1.445</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106.1830611463588</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92.80081818225833</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>-1.435</v>
+      </c>
+      <c r="B30" t="n">
+        <v>81.47587248999739</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="B31" t="n">
+        <v>71.93845262450029</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>-1.425</v>
+      </c>
+      <c r="B32" t="n">
+        <v>63.94356288251656</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57.27051455404681</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>-1.415</v>
+      </c>
+      <c r="B34" t="n">
+        <v>51.72242568882246</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="B35" t="n">
+        <v>47.12548377549497</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>-1.405</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43.32787048359649</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="B37" t="n">
+        <v>40.19834325893321</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>-1.395</v>
+      </c>
+      <c r="B38" t="n">
+        <v>37.62453735902031</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="B39" t="n">
+        <v>35.51108820564725</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>-1.385</v>
+      </c>
+      <c r="B40" t="n">
+        <v>33.63884241936874</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="B41" t="n">
+        <v>31.96206504433876</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>-1.375</v>
+      </c>
+      <c r="B42" t="n">
+        <v>30.60161524403237</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="B43" t="n">
+        <v>29.39764314649552</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>-1.365</v>
+      </c>
+      <c r="B44" t="n">
+        <v>28.28703669155638</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="B45" t="n">
+        <v>27.25681998752706</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>-1.355</v>
+      </c>
+      <c r="B46" t="n">
+        <v>26.29855739718736</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="B47" t="n">
+        <v>25.28004123033313</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>-1.345</v>
+      </c>
+      <c r="B48" t="n">
+        <v>24.25447360977775</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="B49" t="n">
+        <v>23.41921079055743</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>-1.335</v>
+      </c>
+      <c r="B50" t="n">
+        <v>22.7186297693011</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="B51" t="n">
+        <v>22.07927251552352</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>-1.325</v>
+      </c>
+      <c r="B52" t="n">
+        <v>21.49467136034138</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="B53" t="n">
+        <v>20.96344054283819</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>-1.315</v>
+      </c>
+      <c r="B54" t="n">
+        <v>20.48197127903165</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="B55" t="n">
+        <v>20.04803208518428</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="B56" t="n">
+        <v>19.65733997015532</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="B57" t="n">
+        <v>19.30734870114318</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>-1.295</v>
+      </c>
+      <c r="B58" t="n">
+        <v>18.99441737831644</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="B59" t="n">
+        <v>18.71560782783246</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>-1.285</v>
+      </c>
+      <c r="B60" t="n">
+        <v>18.46678853457969</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="B61" t="n">
+        <v>18.2454214552779</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>-1.275</v>
+      </c>
+      <c r="B62" t="n">
+        <v>18.03371170131477</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="B63" t="n">
+        <v>17.78066613117084</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>-1.265</v>
+      </c>
+      <c r="B64" t="n">
+        <v>17.56493948355447</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="B65" t="n">
+        <v>17.38076680300698</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>-1.255</v>
+      </c>
+      <c r="B66" t="n">
+        <v>17.2233792730785</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="B67" t="n">
+        <v>17.08882421766448</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>-1.245</v>
+      </c>
+      <c r="B68" t="n">
+        <v>16.97381864423983</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="B69" t="n">
+        <v>16.87563009455423</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>-1.235</v>
+      </c>
+      <c r="B70" t="n">
+        <v>16.79197968561434</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="B71" t="n">
+        <v>16.72096316120492</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>-1.225</v>
+      </c>
+      <c r="B72" t="n">
+        <v>16.6609865524388</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="B73" t="n">
+        <v>16.61071368673085</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>-1.215</v>
+      </c>
+      <c r="B74" t="n">
+        <v>16.56902330917486</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>-1.21</v>
+      </c>
+      <c r="B75" t="n">
+        <v>16.53497400767677</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>-1.205</v>
+      </c>
+      <c r="B76" t="n">
+        <v>16.50777548016178</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="B77" t="n">
+        <v>16.48676496312016</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>-1.195</v>
+      </c>
+      <c r="B78" t="n">
+        <v>16.47138786782681</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="B79" t="n">
+        <v>16.46118185386553</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>-1.185</v>
+      </c>
+      <c r="B80" t="n">
+        <v>16.4557637174379</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="B81" t="n">
+        <v>16.45481859115869</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>-1.175</v>
+      </c>
+      <c r="B82" t="n">
+        <v>16.45809104818635</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="B83" t="n">
+        <v>16.46537778111046</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>-1.165</v>
+      </c>
+      <c r="B84" t="n">
+        <v>16.47652158865393</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="B85" t="n">
+        <v>16.49140645388478</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>-1.155</v>
+      </c>
+      <c r="B86" t="n">
+        <v>16.50995353862591</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="B87" t="n">
+        <v>16.53211795200765</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>-1.145</v>
+      </c>
+      <c r="B88" t="n">
+        <v>16.5578861781459</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="B89" t="n">
+        <v>16.58727406997919</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>-1.135</v>
+      </c>
+      <c r="B90" t="n">
+        <v>16.62032533434243</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="B91" t="n">
+        <v>16.65711044818552</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>-1.125</v>
+      </c>
+      <c r="B92" t="n">
+        <v>16.69772595809812</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="B93" t="n">
+        <v>16.74229412549021</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>-1.115</v>
+      </c>
+      <c r="B94" t="n">
+        <v>16.79096288831252</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="B95" t="n">
+        <v>16.84390611742044</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>-1.105</v>
+      </c>
+      <c r="B96" t="n">
+        <v>16.90132415185476</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="B97" t="n">
+        <v>16.96344460265828</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>-1.095</v>
+      </c>
+      <c r="B98" t="n">
+        <v>17.03052341954486</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="B99" t="n">
+        <v>17.09806651276294</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>-1.085</v>
+      </c>
+      <c r="B100" t="n">
+        <v>17.15556740815475</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="B101" t="n">
+        <v>17.2175387070144</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>-1.075</v>
+      </c>
+      <c r="B102" t="n">
+        <v>17.28427149915935</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="B103" t="n">
+        <v>17.35608620803816</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>-1.065</v>
+      </c>
+      <c r="B104" t="n">
+        <v>17.43333470428649</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="B105" t="n">
+        <v>17.51640268048319</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>-1.055</v>
+      </c>
+      <c r="B106" t="n">
+        <v>17.60571230447666</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="B107" t="n">
+        <v>17.70172517148384</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>-1.045</v>
+      </c>
+      <c r="B108" t="n">
+        <v>17.80494557811424</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="B109" t="n">
+        <v>17.89476763949873</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>-1.035</v>
+      </c>
+      <c r="B110" t="n">
+        <v>17.98424731272843</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="B111" t="n">
+        <v>18.08060503759432</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>-1.025</v>
+      </c>
+      <c r="B112" t="n">
+        <v>18.18439383899728</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="B113" t="n">
+        <v>18.29621777408005</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>-1.015</v>
+      </c>
+      <c r="B114" t="n">
+        <v>18.41673660959133</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="B115" t="n">
+        <v>18.54667097177341</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>-1.005</v>
+      </c>
+      <c r="B116" t="n">
+        <v>18.67329737063049</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="B117" t="n">
+        <v>18.78805630300553</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>-0.995</v>
+      </c>
+      <c r="B118" t="n">
+        <v>18.91209230039805</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="B119" t="n">
+        <v>19.04621197287803</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>-0.985</v>
+      </c>
+      <c r="B120" t="n">
+        <v>19.19129813940349</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="B121" t="n">
+        <v>19.34831722464444</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>-0.975</v>
+      </c>
+      <c r="B122" t="n">
+        <v>19.51127679052166</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="B123" t="n">
+        <v>19.65297237725546</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>-0.965</v>
+      </c>
+      <c r="B124" t="n">
+        <v>19.80676779701248</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="B125" t="n">
+        <v>19.97377416799586</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>-0.955</v>
+      </c>
+      <c r="B126" t="n">
+        <v>20.15521103192157</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="B127" t="n">
+        <v>20.35241726757468</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>-0.945</v>
+      </c>
+      <c r="B128" t="n">
+        <v>20.53355813644674</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="B129" t="n">
+        <v>20.71610932593659</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>-0.9350000000000001</v>
+      </c>
+      <c r="B130" t="n">
+        <v>20.9151420951312</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="B131" t="n">
+        <v>21.1322434931818</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>-0.925</v>
+      </c>
+      <c r="B132" t="n">
+        <v>21.36916073257251</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="B133" t="n">
+        <v>21.586946175283</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>-0.915</v>
+      </c>
+      <c r="B134" t="n">
+        <v>21.81206439013749</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="B135" t="n">
+        <v>22.05850863029747</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>-0.905</v>
+      </c>
+      <c r="B136" t="n">
+        <v>22.3284134558203</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="B137" t="n">
+        <v>22.60205387373056</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>-0.895</v>
+      </c>
+      <c r="B138" t="n">
+        <v>22.85075318619222</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="B139" t="n">
+        <v>23.12231139262597</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>-0.885</v>
+      </c>
+      <c r="B140" t="n">
+        <v>23.38347820066341</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="B141" t="n">
+        <v>23.64841143826853</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>-0.875</v>
+      </c>
+      <c r="B142" t="n">
+        <v>23.92880501616717</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="B143" t="n">
+        <v>24.23743805052775</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>-0.865</v>
+      </c>
+      <c r="B144" t="n">
+        <v>24.57730870348895</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="B145" t="n">
+        <v>24.95174470084832</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>-0.855</v>
+      </c>
+      <c r="B146" t="n">
+        <v>25.36444039577439</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="B147" t="n">
+        <v>25.80966161881662</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>-0.845</v>
+      </c>
+      <c r="B148" t="n">
+        <v>26.22998106847519</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="B149" t="n">
+        <v>26.69494853503727</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>-0.835</v>
+      </c>
+      <c r="B150" t="n">
+        <v>27.20949397149255</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="B151" t="n">
+        <v>27.77910563351569</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>-0.825</v>
+      </c>
+      <c r="B152" t="n">
+        <v>28.40989442250038</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="B153" t="n">
+        <v>29.10866574544791</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>-0.8149999999999999</v>
+      </c>
+      <c r="B154" t="n">
+        <v>29.88301273892133</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="B155" t="n">
+        <v>30.70130387725088</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>-0.805</v>
+      </c>
+      <c r="B156" t="n">
+        <v>31.50539475032072</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="B157" t="n">
+        <v>32.38150723939981</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>-0.795</v>
+      </c>
+      <c r="B158" t="n">
+        <v>33.33788851733594</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="B159" t="n">
+        <v>34.3833367011356</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>-0.785</v>
+      </c>
+      <c r="B160" t="n">
+        <v>35.52836438751769</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="B161" t="n">
+        <v>36.78135425539178</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>-0.775</v>
+      </c>
+      <c r="B162" t="n">
+        <v>38.15808623677061</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="B163" t="n">
+        <v>39.6715008549957</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>-0.765</v>
+      </c>
+      <c r="B164" t="n">
+        <v>41.33899943976046</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="B165" t="n">
+        <v>43.17721091610066</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>-0.755</v>
+      </c>
+      <c r="B166" t="n">
+        <v>45.20898610205633</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="B167" t="n">
+        <v>47.45731585800534</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>-0.745</v>
+      </c>
+      <c r="B168" t="n">
+        <v>49.96531688493842</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="B169" t="n">
+        <v>52.7699289098704</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>-0.735</v>
+      </c>
+      <c r="B170" t="n">
+        <v>55.90652610871739</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="B171" t="n">
+        <v>59.41472968567668</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>-0.725</v>
+      </c>
+      <c r="B172" t="n">
+        <v>63.33892072304632</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="B173" t="n">
+        <v>67.64644360754237</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>-0.715</v>
+      </c>
+      <c r="B174" t="n">
+        <v>72.37378341587284</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="B175" t="n">
+        <v>77.64791360754643</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>-0.705</v>
+      </c>
+      <c r="B176" t="n">
+        <v>83.53788321961788</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="B177" t="n">
+        <v>90.11903340399364</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>-0.695</v>
+      </c>
+      <c r="B178" t="n">
+        <v>97.47546259607186</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="B179" t="n">
+        <v>105.7035614086144</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>-0.6850000000000001</v>
+      </c>
+      <c r="B180" t="n">
+        <v>114.9095665015554</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="B181" t="n">
+        <v>125.2125605992704</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>-0.675</v>
+      </c>
+      <c r="B182" t="n">
+        <v>136.7477104103261</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="B183" t="n">
+        <v>149.6652133663381</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>-0.665</v>
+      </c>
+      <c r="B184" t="n">
+        <v>164.1336245939482</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="B185" t="n">
+        <v>180.3421085529101</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>-0.655</v>
+      </c>
+      <c r="B186" t="n">
+        <v>198.5029676133406</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="B187" t="n">
+        <v>218.854481757042</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>-0.645</v>
+      </c>
+      <c r="B188" t="n">
+        <v>241.6614562060458</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="B189" t="n">
+        <v>267.2248267945637</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>-0.635</v>
+      </c>
+      <c r="B190" t="n">
+        <v>295.880607009033</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="B191" t="n">
+        <v>328.0029065318657</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="B192" t="n">
+        <v>364.0165349572172</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="B193" t="n">
+        <v>404.3942332081671</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>-0.615</v>
+      </c>
+      <c r="B194" t="n">
+        <v>449.6659524143892</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="B195" t="n">
+        <v>500.4310551555315</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>-0.605</v>
+      </c>
+      <c r="B196" t="n">
+        <v>557.3585345697539</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="B197" t="n">
+        <v>621.1950995258405</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>-0.595</v>
+      </c>
+      <c r="B198" t="n">
+        <v>692.7867605882917</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="B199" t="n">
+        <v>773.0796628250218</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>-0.585</v>
+      </c>
+      <c r="B200" t="n">
+        <v>863.1352411297953</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="B201" t="n">
+        <v>964.144922770544</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>-0.575</v>
+      </c>
+      <c r="B202" t="n">
+        <v>1077.446119778837</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="B203" t="n">
+        <v>1204.540199845093</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>-0.5649999999999999</v>
+      </c>
+      <c r="B204" t="n">
+        <v>1347.11268230519</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="B205" t="n">
+        <v>1507.05593685711</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>-0.555</v>
+      </c>
+      <c r="B206" t="n">
+        <v>1686.494697672828</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="B207" t="n">
+        <v>1887.814745088504</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>-0.545</v>
+      </c>
+      <c r="B208" t="n">
+        <v>2113.695151658802</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="B209" t="n">
+        <v>2367.144539718151</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>printed values</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>source: provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (backward_reachability)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>best cost</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>16.45481859115869</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>best E_N eV</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Fe cost</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>11.51578359717927</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>673 K headroom</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1.02277070031183</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>state-specific max gain</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1.575275488957531</v>
       </c>
     </row>
   </sheetData>
@@ -978,7 +3782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1015,94 +3819,234 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>activity rank vs catalyst-burden rank</t>
+          <t>required recovery vs direct activity multiplier</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: data/rank_preservation_control_v1_1.csv</t>
+          <t>source: analysis/fe_bridge_backward_2026_09_29/nh3_1_2/activity_lifecycle_certified_boundary.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ranks 1-5 in file order on both sides</t>
+          <t>alpha &lt;= 3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>diameter_nm</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>mass_activity_umol_CO_gcat_s</t>
+          <t>required_recovery_pct_10y</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>procurement_burden_vs_best</t>
+          <t>required_recovery_pct_15y</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>required_recovery_pct_20y</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>9.6548</v>
+        <v>99.2506645</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>98.8759967</v>
+      </c>
+      <c r="D5" t="n">
+        <v>98.50132889999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1.022770700312</v>
       </c>
       <c r="B6" t="n">
-        <v>4.4686</v>
+        <v>99.2310499</v>
       </c>
       <c r="C6" t="n">
-        <v>2.161</v>
+        <v>98.8465748</v>
+      </c>
+      <c r="D6" t="n">
+        <v>98.4620998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="B7" t="n">
-        <v>2.5869</v>
+        <v>99.03509219999999</v>
       </c>
       <c r="C7" t="n">
-        <v>3.732</v>
+        <v>98.55263840000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>98.0701845</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="B8" t="n">
-        <v>1.693</v>
+        <v>98.8190768</v>
       </c>
       <c r="C8" t="n">
-        <v>5.703</v>
+        <v>98.22861520000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>97.6381536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>1.575275488958</v>
       </c>
       <c r="B9" t="n">
-        <v>1.1973</v>
+        <v>98.75395810000001</v>
       </c>
       <c r="C9" t="n">
-        <v>8.064</v>
+        <v>98.13093720000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>97.50791629999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98.60268789999999</v>
+      </c>
+      <c r="C10" t="n">
+        <v>97.9040318</v>
+      </c>
+      <c r="D10" t="n">
+        <v>97.20537569999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98.3859824</v>
+      </c>
+      <c r="C11" t="n">
+        <v>97.57897370000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>96.7719649</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98.1690059</v>
+      </c>
+      <c r="C12" t="n">
+        <v>97.25350880000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>96.3380118</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97.5167776</v>
+      </c>
+      <c r="C13" t="n">
+        <v>96.2751664</v>
+      </c>
+      <c r="D13" t="n">
+        <v>95.0335552</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>targets at 99 % recovery</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>source: analysis/fe_bridge_backward_2026_09_29/nh3_1_2/activity_lifecycle_target_keypoints.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>catalyst_life_y</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Ru_recovery_fraction</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>certified_upper_bound_required_direct_activity_multiplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.290645757</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.903973414</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.710093177</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +4060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1153,457 +4097,187 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mass activity and required catalyst vs diameter</t>
+          <t>exact strict-scaling lifecycle boundary</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>source: data/rank_preservation_control_v1_1.csv</t>
+          <t>source: analysis/fe_bridge_backward_2026_09_29/nh3_1_2/scaling_lifecycle_exact_global_boundary.csv</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>diameter_nm</t>
+          <t>life_y</t>
         </is>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>mass_activity_umol_CO_gcat_s</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>required_catalyst_mass_mg</t>
+          <t>required_recovery_percent</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>9.6548</v>
-      </c>
-      <c r="C4" t="n">
-        <v>19.505</v>
+        <v>99.58744856913955</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>4.4686</v>
-      </c>
-      <c r="C5" t="n">
-        <v>42.143</v>
+        <v>99.17489713827914</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>2.5869</v>
-      </c>
-      <c r="C6" t="n">
-        <v>72.797</v>
+        <v>98.7623457074187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>1.693</v>
-      </c>
-      <c r="C7" t="n">
-        <v>111.235</v>
+        <v>98.34979427655828</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B8" t="n">
-        <v>1.1973</v>
-      </c>
-      <c r="C8" t="n">
-        <v>157.284</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>exact order kept, semi-open extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>source: data/rank_preservation_semiopen_v1_3_summary.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>window</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>stress</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>full_preservation_fraction</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>primary_273_293K</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>mild</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="D4" t="n">
-        <v>99.90000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>primary_273_293K</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9216</v>
-      </c>
-      <c r="D5" t="n">
-        <v>92.16</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>primary_273_293K</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6429</v>
-      </c>
-      <c r="D6" t="n">
-        <v>64.29000000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>sensitivity_273_313K</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mild</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.9510999999999999</v>
-      </c>
-      <c r="D7" t="n">
-        <v>95.11</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>sensitivity_273_313K</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>moderate</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7262</v>
-      </c>
-      <c r="D8" t="n">
-        <v>72.61999999999999</v>
+        <v>97.93724284569784</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sensitivity_273_313K</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.4306</v>
-      </c>
-      <c r="D9" t="n">
-        <v>43.06</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="16" customWidth="1" min="25" max="25"/>
-    <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>upstream-to-downstream Spearman rho</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>source: see column source</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>system</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>rho</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NH3, all 15 metals</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.9107142857142855</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (deterministic.rolling) (K = 15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NH3, frontier top 3</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>provenance/nh3_final_1_2/source_harness/outputs/nh3_final_1_2_20261013/results.json (deterministic.rolling) (K = 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MeOH, 4 states, 2 % purge</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>data/meoh/meoh_candidate_ranking_D01v3_provenance.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MeOH, min over purge 0.5-40 %</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>data/meoh/meoh_purge_robustness_D01v3.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MeOH, max over purge 0.5-40 %</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>data/meoh/meoh_purge_robustness_D01v3.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Au/TiO2, 5 sizes</t>
-        </is>
+      <c r="A9" t="n">
+        <v>30</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>docs/RANK_PRESERVATION_CONTROL_V1_1_RESULT.md (rho = 1.000; the ranks in data/rank_preservation_control_v1_1.csv are identical)</t>
-        </is>
+        <v>97.52469141483742</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Au/TiO2, semi-open moderate, mean</t>
-        </is>
+      <c r="A10" t="n">
+        <v>40</v>
       </c>
       <c r="B10" t="n">
-        <v>0.99214</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>data/rank_preservation_semiopen_v1_3_summary.csv (primary_273_293K, moderate)</t>
-        </is>
+        <v>96.69958855311656</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>50</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95.87448569139571</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tested box and parity points</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>source: analysis/fe_bridge_backward_2026_09_29/nh3_1_2/scaling_lifecycle_exact_summary.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tested box: max life (y)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tested box: max recovery (%)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>best-corner margin vs Fe USD/t</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.3167362919996659</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>best-corner cost USD/t</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11.1990473051796</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>required recovery at 20 y (%)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>98.34979427655827</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>required life at 99 % recovery (y)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12.11970102629835</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>critical lifecycle factor q* (1/y)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0008251028617208592</v>
       </c>
     </row>
   </sheetData>
